--- a/合同生成/templates/合同模板/合同模板.xlsx
+++ b/合同生成/templates/合同模板/合同模板.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
   <si>
     <t>绍兴宏邦电子科技有限公司  采购合同</t>
   </si>
@@ -38,43 +38,19 @@
     <t>采购单号：</t>
   </si>
   <si>
-    <t>HB20260328-001</t>
-  </si>
-  <si>
     <t>制表日期：</t>
   </si>
   <si>
-    <t>2026/3/28</t>
-  </si>
-  <si>
     <t>买方：</t>
   </si>
   <si>
-    <t>绍兴宏邦电子科技有限公司</t>
-  </si>
-  <si>
     <t>卖方：</t>
   </si>
   <si>
-    <t>绍兴宏邦电子科技有限公司昂氏（上海）电子贸易有限公司</t>
-  </si>
-  <si>
     <t>地址：</t>
   </si>
   <si>
-    <t>浙江绍兴市越城区皋埠街道银山路167号</t>
-  </si>
-  <si>
-    <t>上海市长宁区娄山关路555号2506-10室</t>
-  </si>
-  <si>
     <t>电话：</t>
-  </si>
-  <si>
-    <t>0575-85127680</t>
-  </si>
-  <si>
-    <t>021-22194000-4148</t>
   </si>
   <si>
     <t>序号</t>
@@ -1265,87 +1241,71 @@
         <v>1</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
-        <v>2</v>
-      </c>
+      <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="6"/>
-      <c r="L3" s="2" t="s">
-        <v>4</v>
-      </c>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3"/>
-      <c r="C4" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="C4" s="7"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="6"/>
       <c r="I4" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="3"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="7" t="s">
-        <v>10</v>
-      </c>
+      <c r="C5" s="7"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="6"/>
       <c r="I5" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="7" t="s">
-        <v>13</v>
-      </c>
+      <c r="C6" s="7"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="6"/>
       <c r="I6" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="3"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:12">
@@ -1364,40 +1324,40 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:12">
       <c r="A8" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="J8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="K8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="L8" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:12">
@@ -1436,7 +1396,7 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:12">
       <c r="A11" s="13" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1455,7 +1415,7 @@
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:12">
       <c r="A12" s="15" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1471,7 +1431,7 @@
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:12">
       <c r="A13" s="16" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1487,7 +1447,7 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:12">
       <c r="A14" s="16" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1503,7 +1463,7 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:12">
       <c r="A15" s="16" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1519,7 +1479,7 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:12">
       <c r="A16" s="16" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1535,7 +1495,7 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:12">
       <c r="A17" s="16" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1551,7 +1511,7 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:12">
       <c r="A18" s="16" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1567,7 +1527,7 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:12">
       <c r="A19" s="16" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1597,7 +1557,7 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:12">
       <c r="A21" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1606,7 +1566,7 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -1615,7 +1575,7 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:12">
       <c r="A22" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1624,7 +1584,7 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -1633,7 +1593,7 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:12">
       <c r="A23" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1642,7 +1602,7 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
